--- a/timesheet/pithambar_timesheet.xlsx
+++ b/timesheet/pithambar_timesheet.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="6">
   <si>
     <t>Date</t>
   </si>
@@ -38,10 +38,10 @@
     <t>Hours</t>
   </si>
   <si>
-    <t/>
+    <t>Set up GitHub,vscode, google meet , and the internship repository.</t>
   </si>
   <si>
-    <t>Set up GitHub,vscode, google meet , and the internship repository.</t>
+    <t/>
   </si>
   <si>
     <t>Total Hours</t>
@@ -703,7 +703,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1250,8 +1250,8 @@
       <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
+      <c r="C2" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1259,10 +1259,10 @@
         <v>46313</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1270,10 +1270,10 @@
         <v>46314</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1281,10 +1281,10 @@
         <v>46315</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1292,10 +1292,10 @@
         <v>46316</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1303,32 +1303,26 @@
         <v>46317</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3">
         <v>46318</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1">
-        <v>4</v>
-      </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3">
         <v>46319</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1336,10 +1330,10 @@
         <v>46320</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1347,10 +1341,10 @@
         <v>46321</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1358,10 +1352,10 @@
         <v>46322</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1369,10 +1363,10 @@
         <v>46323</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1380,10 +1374,10 @@
         <v>46324</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1391,10 +1385,10 @@
         <v>46325</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1402,10 +1396,10 @@
         <v>46326</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1413,10 +1407,10 @@
         <v>46327</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1424,10 +1418,10 @@
         <v>46328</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1435,10 +1429,10 @@
         <v>46329</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1446,10 +1440,10 @@
         <v>46330</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1457,10 +1451,10 @@
         <v>46331</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1468,10 +1462,10 @@
         <v>46332</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1479,10 +1473,10 @@
         <v>46333</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1490,10 +1484,10 @@
         <v>46334</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1501,10 +1495,10 @@
         <v>46335</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1512,10 +1506,10 @@
         <v>46336</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1523,10 +1517,10 @@
         <v>46337</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1534,10 +1528,10 @@
         <v>46338</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1545,10 +1539,10 @@
         <v>46339</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1556,10 +1550,10 @@
         <v>46340</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1567,10 +1561,10 @@
         <v>46341</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1578,10 +1572,10 @@
         <v>46342</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1589,10 +1583,10 @@
         <v>46343</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:3">

--- a/timesheet/pithambar_timesheet.xlsx
+++ b/timesheet/pithambar_timesheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView windowWidth="22188" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="pithambar_timesheet" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="7">
   <si>
     <t>Date</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>Set up GitHub,vscode, google meet , and the internship repository.</t>
+  </si>
+  <si>
+    <t>researched two good and bad charts and pushed it in github, and gave information</t>
   </si>
   <si>
     <t/>
@@ -1227,7 +1230,7 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
-    <col min="2" max="2" width="56.8888888888889" style="1" customWidth="1"/>
+    <col min="2" max="2" width="74.4444444444444" style="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" customWidth="1"/>
     <col min="4" max="16384" width="10" style="1"/>
   </cols>
@@ -1261,7 +1264,7 @@
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="1">
         <v>4</v>
       </c>
     </row>
@@ -1270,10 +1273,10 @@
         <v>46314</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1281,10 +1284,10 @@
         <v>46315</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1292,10 +1295,10 @@
         <v>46316</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1303,10 +1306,10 @@
         <v>46317</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1319,10 +1322,10 @@
         <v>46319</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1330,10 +1333,10 @@
         <v>46320</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1341,10 +1344,10 @@
         <v>46321</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1352,10 +1355,10 @@
         <v>46322</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1363,10 +1366,10 @@
         <v>46323</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1374,10 +1377,10 @@
         <v>46324</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1385,10 +1388,10 @@
         <v>46325</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1396,10 +1399,10 @@
         <v>46326</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1407,10 +1410,10 @@
         <v>46327</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1418,10 +1421,10 @@
         <v>46328</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1429,10 +1432,10 @@
         <v>46329</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1440,10 +1443,10 @@
         <v>46330</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1451,10 +1454,10 @@
         <v>46331</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1462,10 +1465,10 @@
         <v>46332</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1473,10 +1476,10 @@
         <v>46333</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1484,10 +1487,10 @@
         <v>46334</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1495,10 +1498,10 @@
         <v>46335</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1506,10 +1509,10 @@
         <v>46336</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1517,10 +1520,10 @@
         <v>46337</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1528,10 +1531,10 @@
         <v>46338</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1539,10 +1542,10 @@
         <v>46339</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1550,10 +1553,10 @@
         <v>46340</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1561,10 +1564,10 @@
         <v>46341</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1572,10 +1575,10 @@
         <v>46342</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1583,16 +1586,16 @@
         <v>46343</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="4">
         <v>0</v>

--- a/timesheet/pithambar_timesheet.xlsx
+++ b/timesheet/pithambar_timesheet.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94afc5e5a658c2e0/Documents/GitHub/mvj-internship-dataviz-team1/timesheet/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_E5AECC59E9DF62B417BE5BD2E3105C4D772813EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{287E5642-9EA6-44E8-944C-D3E224A71DB0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="pithambar_timesheet" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="6">
   <si>
     <t>Date</t>
   </si>
@@ -47,20 +41,24 @@
     <t/>
   </si>
   <si>
-    <t>Total Hours</t>
+    <t>Set up GitHub,vscode, google meet , and the internship repository.</t>
   </si>
   <si>
-    <t>gfgcbiubibj</t>
+    <t>Total Hours</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mmm/yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="dd/mmm/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,21 +67,158 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -102,8 +237,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -111,9 +432,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -121,165 +684,96 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -290,7 +784,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -318,47 +812,157 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -613,17 +1217,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
-    <col min="2" max="2" width="48" style="1" customWidth="1"/>
+    <col min="2" max="2" width="56.8888888888889" style="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="1" customWidth="1"/>
     <col min="4" max="16384" width="10" style="1"/>
   </cols>
@@ -710,10 +1314,10 @@
         <v>46318</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="C8" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -994,7 +1598,7 @@
     <row r="34" spans="1:3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" s="4">
         <v>0</v>
@@ -1002,5 +1606,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/timesheet/pithambar_timesheet.xlsx
+++ b/timesheet/pithambar_timesheet.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8400"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="pithambar_timesheet" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="8">
   <si>
     <t>Date</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>researched two good and bad charts and pushed it in github, and gave information</t>
+  </si>
+  <si>
+    <t>collected 3 questions and created a chart choices</t>
   </si>
   <si>
     <t/>
@@ -1275,8 +1278,8 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
+      <c r="C4" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1284,10 +1287,10 @@
         <v>46315</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1295,10 +1298,10 @@
         <v>46316</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1306,10 +1309,10 @@
         <v>46317</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1322,10 +1325,10 @@
         <v>46319</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1333,10 +1336,10 @@
         <v>46320</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1344,10 +1347,10 @@
         <v>46321</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1355,10 +1358,10 @@
         <v>46322</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1366,10 +1369,10 @@
         <v>46323</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1377,10 +1380,10 @@
         <v>46324</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1388,10 +1391,10 @@
         <v>46325</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1399,10 +1402,10 @@
         <v>46326</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1410,10 +1413,10 @@
         <v>46327</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1421,10 +1424,10 @@
         <v>46328</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1432,10 +1435,10 @@
         <v>46329</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1443,10 +1446,10 @@
         <v>46330</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1454,10 +1457,10 @@
         <v>46331</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1465,10 +1468,10 @@
         <v>46332</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1476,10 +1479,10 @@
         <v>46333</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1487,10 +1490,10 @@
         <v>46334</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1498,10 +1501,10 @@
         <v>46335</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1509,10 +1512,10 @@
         <v>46336</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1520,10 +1523,10 @@
         <v>46337</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1531,10 +1534,10 @@
         <v>46338</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1542,10 +1545,10 @@
         <v>46339</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1553,10 +1556,10 @@
         <v>46340</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1564,10 +1567,10 @@
         <v>46341</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1575,10 +1578,10 @@
         <v>46342</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1586,16 +1589,16 @@
         <v>46343</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34" s="4">
         <v>0</v>

--- a/timesheet/pithambar_timesheet.xlsx
+++ b/timesheet/pithambar_timesheet.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="11">
   <si>
     <t>Date</t>
   </si>
@@ -47,7 +47,16 @@
     <t>collected 3 questions and created a chart choices</t>
   </si>
   <si>
+    <t>remade 1 bad chart into good chart makeover</t>
+  </si>
+  <si>
+    <t>cleaned banglore rainfall data and made dashboard</t>
+  </si>
+  <si>
     <t/>
+  </si>
+  <si>
+    <t>cleaning and merging namma metro raidership</t>
   </si>
   <si>
     <t>Total Hours</t>
@@ -1289,8 +1298,8 @@
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>6</v>
+      <c r="C5" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1298,10 +1307,10 @@
         <v>46316</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1309,10 +1318,10 @@
         <v>46317</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1325,10 +1334,10 @@
         <v>46319</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1336,10 +1345,10 @@
         <v>46320</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -1347,10 +1356,10 @@
         <v>46321</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1358,10 +1367,10 @@
         <v>46322</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1369,10 +1378,10 @@
         <v>46323</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1380,10 +1389,10 @@
         <v>46324</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1391,10 +1400,10 @@
         <v>46325</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1402,10 +1411,10 @@
         <v>46326</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1413,10 +1422,10 @@
         <v>46327</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1424,10 +1433,10 @@
         <v>46328</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1435,10 +1444,10 @@
         <v>46329</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1446,10 +1455,10 @@
         <v>46330</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1457,10 +1466,10 @@
         <v>46331</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1468,10 +1477,10 @@
         <v>46332</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1479,10 +1488,10 @@
         <v>46333</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1490,10 +1499,10 @@
         <v>46334</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1501,10 +1510,10 @@
         <v>46335</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1512,10 +1521,10 @@
         <v>46336</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1523,10 +1532,10 @@
         <v>46337</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1534,10 +1543,10 @@
         <v>46338</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1545,10 +1554,10 @@
         <v>46339</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1556,10 +1565,10 @@
         <v>46340</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1567,10 +1576,10 @@
         <v>46341</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1578,10 +1587,10 @@
         <v>46342</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1589,16 +1598,16 @@
         <v>46343</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C34" s="4">
         <v>0</v>
